--- a/data/data_dictionary.xlsx
+++ b/data/data_dictionary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Unique identifier for each transaction line item in an order</t>
+          <t>Unique line item identifier</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Identifier linking items purchased in the same customer checkout session</t>
+          <t>Checkout order session identifier</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Date when the order transaction was completed (YYYY-MM-DD)</t>
+          <t>Date of transaction (2021 to 2026)</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Unique identifier of the customer who placed the order</t>
+          <t>Purchasing customer identifier</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Unique identifier of the product item purchased</t>
+          <t>Purchased SKU identifier</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Units of the product purchased in the transaction line item</t>
+          <t>Units of product purchased</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Standard catalog retail selling price per single unit in INR (₹)</t>
+          <t>Retail catalog price in ₹</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Discount rate applied to the line item (0.00 to 0.25)</t>
+          <t>Discount rate applied (0.00 to 0.20)</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cost of Goods Sold: Quantity * Unit Cost</t>
+          <t>Cost of goods: Quantity * Unit Cost</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gross profit generated: Sales Amount - Cost Amount</t>
+          <t>Gross profit: Sales Amount - Cost Amount</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Payment method used (UPI, Credit Card, Debit Card, Net Banking, COD, EMI)</t>
+          <t>Payment method (UPI, Card, Net Banking, COD)</t>
         </is>
       </c>
     </row>
@@ -790,736 +790,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Geographic delivery fulfillment region identifier</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>dim_customer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>customer_id</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>VARCHAR(20)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Unique customer primary key</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>dim_customer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>customer_name</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>VARCHAR(100)</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Full name of the registered customer</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>dim_customer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>gender</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>VARCHAR(10)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Customer gender (Male, Female, Other)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>dim_customer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Customer age in years (18 to 72)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>dim_customer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>VARCHAR(50)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Customer registered residence city</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>dim_customer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>region_id</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>VARCHAR(10)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Regional zone identifier for the customer residence</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>dim_customer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>signup_date</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Account registration date (YYYY-MM-DD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>dim_customer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>customer_segment</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>VARCHAR(30)</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Account classification (Consumer, Corporate, Small Business)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>dim_product</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>product_id</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>VARCHAR(20)</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Unique product primary key</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>dim_product</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>product_name</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>VARCHAR(150)</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Descriptive brand and model name of the product</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>dim_product</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>VARCHAR(50)</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Top-level retail merchandise category (12 categories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>dim_product</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>subcategory</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>VARCHAR(50)</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Granular product subcategory (45+ subcategories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>dim_product</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>VARCHAR(50)</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Brand / Manufacturer name</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>dim_product</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>unit_cost</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>NUMERIC(10,2)</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Unit wholesale manufacturing/acquisition cost in INR (₹)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>dim_product</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>unit_price</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>NUMERIC(10,2)</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Unit retail catalog price in INR (₹)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>dim_region</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>region_id</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>VARCHAR(10)</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Unique geographic region primary key</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>dim_region</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>region_name</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>VARCHAR(50)</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Commercial sales operational territory (West, North, South, East, Central, North-East)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>dim_region</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>VARCHAR(100)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>States covered under the sales region</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>dim_region</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>zone</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>VARCHAR(50)</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Macro geopolitical zone in India</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>dim_date</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Calendar calendar date (YYYY-MM-DD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>dim_date</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Calendar year (2024, 2025)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dim_date</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>quarter</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>VARCHAR(5)</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Financial calendar quarter (Q1, Q2, Q3, Q4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dim_date</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>VARCHAR(20)</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Full month name (January to December)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>dim_date</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>month_number</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Month sequence index (1 to 12)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>dim_date</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>week</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>ISO calendar week of the year (1 to 53)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>dim_date</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Day of the month (1 to 31)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>dim_date</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>day_name</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>VARCHAR(15)</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Name of the day of the week (Monday to Sunday)</t>
+          <t>Delivery fulfillment territory</t>
         </is>
       </c>
     </row>
